--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/25.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/25.xlsx
@@ -426,13 +426,13 @@
         <v>-10.43027698028729</v>
       </c>
       <c r="E2">
-        <v>-17.37841505838126</v>
+        <v>-14.16858286853043</v>
       </c>
       <c r="F2">
-        <v>-2.342893210137822</v>
+        <v>-2.432555697816841</v>
       </c>
       <c r="G2">
-        <v>-8.159714616224543</v>
+        <v>-6.465976617968156</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.5276464612012</v>
       </c>
       <c r="E3">
-        <v>-18.49655868951119</v>
+        <v>-15.26655667643019</v>
       </c>
       <c r="F3">
-        <v>-2.377906643519352</v>
+        <v>-2.46882659291582</v>
       </c>
       <c r="G3">
-        <v>-8.649453549485546</v>
+        <v>-6.68308881552464</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.64858991220815</v>
       </c>
       <c r="E4">
-        <v>-18.38808815160546</v>
+        <v>-16.2381634171459</v>
       </c>
       <c r="F4">
-        <v>-2.467728177739708</v>
+        <v>-2.608703055817739</v>
       </c>
       <c r="G4">
-        <v>-7.866873689457231</v>
+        <v>-6.852068991485659</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.75297480734961</v>
       </c>
       <c r="E5">
-        <v>-18.610984170737</v>
+        <v>-16.91523367992873</v>
       </c>
       <c r="F5">
-        <v>-2.521974645479436</v>
+        <v>-2.382938975491359</v>
       </c>
       <c r="G5">
-        <v>-7.996660316778819</v>
+        <v>-7.655813169146535</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.81400866044548</v>
       </c>
       <c r="E6">
-        <v>-18.87791959959313</v>
+        <v>-17.64528256012729</v>
       </c>
       <c r="F6">
-        <v>-2.532740936613621</v>
+        <v>-2.355903548566191</v>
       </c>
       <c r="G6">
-        <v>-7.971927231054923</v>
+        <v>-6.872584442192522</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.79373413818827</v>
       </c>
       <c r="E7">
-        <v>-20.43507161492265</v>
+        <v>-18.18680201043852</v>
       </c>
       <c r="F7">
-        <v>-2.447284898606019</v>
+        <v>-2.156913131065694</v>
       </c>
       <c r="G7">
-        <v>-8.092235766497577</v>
+        <v>-6.648066554264689</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.66738993063341</v>
       </c>
       <c r="E8">
-        <v>-21.35936033073222</v>
+        <v>-19.39086890738997</v>
       </c>
       <c r="F8">
-        <v>-2.638834091727168</v>
+        <v>-2.456459895959426</v>
       </c>
       <c r="G8">
-        <v>-7.3920620060328</v>
+        <v>-6.115744073732039</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.41510502855715</v>
       </c>
       <c r="E9">
-        <v>-21.81553163142088</v>
+        <v>-19.78300305713617</v>
       </c>
       <c r="F9">
-        <v>-2.769481713394498</v>
+        <v>-1.937023832359968</v>
       </c>
       <c r="G9">
-        <v>-7.497976289470703</v>
+        <v>-6.148928982217694</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.0272943851846</v>
       </c>
       <c r="E10">
-        <v>-22.61954407758672</v>
+        <v>-19.89750552242012</v>
       </c>
       <c r="F10">
-        <v>-2.632627963145394</v>
+        <v>-1.905170620620119</v>
       </c>
       <c r="G10">
-        <v>-7.463983607873466</v>
+        <v>-5.731631406447022</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.51585352738687</v>
       </c>
       <c r="E11">
-        <v>-22.9517982155295</v>
+        <v>-20.96844434049408</v>
       </c>
       <c r="F11">
-        <v>-2.391605355259447</v>
+        <v>-1.885329564588265</v>
       </c>
       <c r="G11">
-        <v>-6.896652108263024</v>
+        <v>-5.442816103055464</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.902603280364048</v>
       </c>
       <c r="E12">
-        <v>-24.074420507453</v>
+        <v>-22.58921688715736</v>
       </c>
       <c r="F12">
-        <v>-2.081513473328077</v>
+        <v>-1.818264111290214</v>
       </c>
       <c r="G12">
-        <v>-6.6620105720761</v>
+        <v>-4.900297142261859</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.222833169296241</v>
       </c>
       <c r="E13">
-        <v>-25.20033499998008</v>
+        <v>-22.88835429468203</v>
       </c>
       <c r="F13">
-        <v>-1.979834688104049</v>
+        <v>-2.136868296652751</v>
       </c>
       <c r="G13">
-        <v>-6.415785437047266</v>
+        <v>-4.442574494911146</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.531850255881921</v>
       </c>
       <c r="E14">
-        <v>-26.11250099087112</v>
+        <v>-23.16989858068692</v>
       </c>
       <c r="F14">
-        <v>-1.815761613366357</v>
+        <v>-1.115110239995673</v>
       </c>
       <c r="G14">
-        <v>-6.185781975160861</v>
+        <v>-4.254515645007308</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.880556472709208</v>
       </c>
       <c r="E15">
-        <v>-26.7373579483455</v>
+        <v>-23.94194452883261</v>
       </c>
       <c r="F15">
-        <v>-1.64189309409056</v>
+        <v>-1.031505603133328</v>
       </c>
       <c r="G15">
-        <v>-5.255667653174925</v>
+        <v>-4.08893539931512</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.326465452930589</v>
       </c>
       <c r="E16">
-        <v>-26.59455252051362</v>
+        <v>-25.34062712473771</v>
       </c>
       <c r="F16">
-        <v>-1.447825664064901</v>
+        <v>-0.8743535380460251</v>
       </c>
       <c r="G16">
-        <v>-5.344032734709152</v>
+        <v>-3.400312132236859</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.913875654116409</v>
       </c>
       <c r="E17">
-        <v>-29.11312221004158</v>
+        <v>-25.66782748568792</v>
       </c>
       <c r="F17">
-        <v>-0.866243821172618</v>
+        <v>-0.8149405428150361</v>
       </c>
       <c r="G17">
-        <v>-4.794700671195726</v>
+        <v>-3.536448385902769</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.673973967812843</v>
       </c>
       <c r="E18">
-        <v>-29.67395107352152</v>
+        <v>-27.24279904623762</v>
       </c>
       <c r="F18">
-        <v>-0.9662020873010315</v>
+        <v>-0.4641029250747644</v>
       </c>
       <c r="G18">
-        <v>-4.773850855389396</v>
+        <v>-3.027551325606002</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.625590186004164</v>
       </c>
       <c r="E19">
-        <v>-30.06873664479921</v>
+        <v>-28.13459596104215</v>
       </c>
       <c r="F19">
-        <v>-0.5189822655102316</v>
+        <v>0.08406506189079448</v>
       </c>
       <c r="G19">
-        <v>-5.134200426793526</v>
+        <v>-2.99340304836842</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.761316528268684</v>
       </c>
       <c r="E20">
-        <v>-30.11868797734082</v>
+        <v>-28.63488818398755</v>
       </c>
       <c r="F20">
-        <v>-0.4045499357527023</v>
+        <v>0.3718597784410099</v>
       </c>
       <c r="G20">
-        <v>-5.080526551965322</v>
+        <v>-2.234639252949621</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.060906534679985</v>
       </c>
       <c r="E21">
-        <v>-31.10694138850873</v>
+        <v>-29.32259130374038</v>
       </c>
       <c r="F21">
-        <v>-0.2220042679325809</v>
+        <v>0.3459053709764958</v>
       </c>
       <c r="G21">
-        <v>-4.434566285251649</v>
+        <v>-2.936335864362463</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.495181061499453</v>
       </c>
       <c r="E22">
-        <v>-31.65206097565606</v>
+        <v>-29.67646664083278</v>
       </c>
       <c r="F22">
-        <v>0.1679662542833424</v>
+        <v>0.3994775476503454</v>
       </c>
       <c r="G22">
-        <v>-4.824088383947837</v>
+        <v>-2.907789030177327</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.018932301077253</v>
       </c>
       <c r="E23">
-        <v>-32.34931238285407</v>
+        <v>-29.81062494754702</v>
       </c>
       <c r="F23">
-        <v>0.4611171944600594</v>
+        <v>0.8258597874237238</v>
       </c>
       <c r="G23">
-        <v>-4.559698285545021</v>
+        <v>-3.054697799028026</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.586758779870181</v>
       </c>
       <c r="E24">
-        <v>-31.98580951002136</v>
+        <v>-29.92539459279742</v>
       </c>
       <c r="F24">
-        <v>0.4754786001223945</v>
+        <v>0.7673671083772451</v>
       </c>
       <c r="G24">
-        <v>-5.354186177878096</v>
+        <v>-2.772467170714079</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.144613248600733</v>
       </c>
       <c r="E25">
-        <v>-32.35772402332331</v>
+        <v>-30.62972174063241</v>
       </c>
       <c r="F25">
-        <v>0.6449973621660909</v>
+        <v>0.5959977735556945</v>
       </c>
       <c r="G25">
-        <v>-4.856892579696475</v>
+        <v>-2.522375318495376</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.643812453621486</v>
       </c>
       <c r="E26">
-        <v>-32.57077966843619</v>
+        <v>-30.98402049004453</v>
       </c>
       <c r="F26">
-        <v>0.6117143882890096</v>
+        <v>0.9212843987566156</v>
       </c>
       <c r="G26">
-        <v>-4.998481301865564</v>
+        <v>-2.403990210011038</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.043020960691033</v>
       </c>
       <c r="E27">
-        <v>-32.76055442867563</v>
+        <v>-30.94015316233222</v>
       </c>
       <c r="F27">
-        <v>0.1927675743231596</v>
+        <v>0.7021944745945912</v>
       </c>
       <c r="G27">
-        <v>-5.079500282848148</v>
+        <v>-3.106034428705504</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.304481756369192</v>
       </c>
       <c r="E28">
-        <v>-33.56819418252162</v>
+        <v>-30.49024021272216</v>
       </c>
       <c r="F28">
-        <v>0.4430256503829182</v>
+        <v>0.710599090263395</v>
       </c>
       <c r="G28">
-        <v>-4.645981033935047</v>
+        <v>-3.653942957637043</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.403937532432609</v>
       </c>
       <c r="E29">
-        <v>-32.46310614195581</v>
+        <v>-30.55115724507334</v>
       </c>
       <c r="F29">
-        <v>0.2147466466216389</v>
+        <v>0.5396058342427154</v>
       </c>
       <c r="G29">
-        <v>-4.879063303172973</v>
+        <v>-3.551266387736547</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.331980278383725</v>
       </c>
       <c r="E30">
-        <v>-32.02214824969591</v>
+        <v>-30.54908093974082</v>
       </c>
       <c r="F30">
-        <v>0.3234715249738796</v>
+        <v>0.8196072702673931</v>
       </c>
       <c r="G30">
-        <v>-5.093447611205097</v>
+        <v>-3.676090507294767</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.089527089486655</v>
       </c>
       <c r="E31">
-        <v>-32.30835007121768</v>
+        <v>-30.93524429650791</v>
       </c>
       <c r="F31">
-        <v>-0.02568533530611202</v>
+        <v>0.6797175534870293</v>
       </c>
       <c r="G31">
-        <v>-4.620261405640449</v>
+        <v>-3.421231469499514</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.694157136328</v>
       </c>
       <c r="E32">
-        <v>-31.69267685903085</v>
+        <v>-29.94721957327739</v>
       </c>
       <c r="F32">
-        <v>-0.2305886393277921</v>
+        <v>0.3256981765526047</v>
       </c>
       <c r="G32">
-        <v>-4.418642561207755</v>
+        <v>-2.551743167974251</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.173121311858775</v>
       </c>
       <c r="E33">
-        <v>-31.7399337495379</v>
+        <v>-30.02915325349817</v>
       </c>
       <c r="F33">
-        <v>-0.2896885116805228</v>
+        <v>0.645525860569077</v>
       </c>
       <c r="G33">
-        <v>-4.301104952381471</v>
+        <v>-3.211908985596936</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.561962629382201</v>
       </c>
       <c r="E34">
-        <v>-31.09350087765396</v>
+        <v>-29.93841848404348</v>
       </c>
       <c r="F34">
-        <v>0.3302136072652648</v>
+        <v>0.409254768105588</v>
       </c>
       <c r="G34">
-        <v>-3.755679332604386</v>
+        <v>-3.226412485604483</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.906574773241357</v>
       </c>
       <c r="E35">
-        <v>-30.1466626255232</v>
+        <v>-28.70537388191694</v>
       </c>
       <c r="F35">
-        <v>0.1240346174432734</v>
+        <v>0.5464506340920477</v>
       </c>
       <c r="G35">
-        <v>-4.53558758238251</v>
+        <v>-2.045057552097717</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.248255369186958</v>
       </c>
       <c r="E36">
-        <v>-30.51734086542106</v>
+        <v>-28.62585840681626</v>
       </c>
       <c r="F36">
-        <v>0.193682920303253</v>
+        <v>0.3317154373665403</v>
       </c>
       <c r="G36">
-        <v>-4.984153260771598</v>
+        <v>-2.86403354978478</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.625610732863823</v>
       </c>
       <c r="E37">
-        <v>-30.22610564503976</v>
+        <v>-28.49054307499306</v>
       </c>
       <c r="F37">
-        <v>0.2898497488290532</v>
+        <v>0.6456385185358577</v>
       </c>
       <c r="G37">
-        <v>-3.537769293572938</v>
+        <v>-2.484648341529842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.077078152546204</v>
       </c>
       <c r="E38">
-        <v>-29.06804125129523</v>
+        <v>-27.52972315936362</v>
       </c>
       <c r="F38">
-        <v>0.1071110714040795</v>
+        <v>0.4607021823912569</v>
       </c>
       <c r="G38">
-        <v>-3.388212088290823</v>
+        <v>-2.270141543312765</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.626316161560622</v>
       </c>
       <c r="E39">
-        <v>-30.05321303590092</v>
+        <v>-26.77540165848394</v>
       </c>
       <c r="F39">
-        <v>0.09199253793558575</v>
+        <v>0.5599422539814433</v>
       </c>
       <c r="G39">
-        <v>-3.952080757267188</v>
+        <v>-2.18117725303593</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.29406474952429</v>
       </c>
       <c r="E40">
-        <v>-29.72988678446427</v>
+        <v>-27.23237449907196</v>
       </c>
       <c r="F40">
-        <v>-0.08821050686941871</v>
+        <v>0.3936897446069853</v>
       </c>
       <c r="G40">
-        <v>-3.864788292487685</v>
+        <v>-2.514036054281952</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.087393306344608</v>
       </c>
       <c r="E41">
-        <v>-28.30960789601659</v>
+        <v>-26.79991428828746</v>
       </c>
       <c r="F41">
-        <v>-0.03956545950742054</v>
+        <v>0.5297350082709565</v>
       </c>
       <c r="G41">
-        <v>-3.667324182706777</v>
+        <v>-2.081231883205333</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.003528564066901</v>
       </c>
       <c r="E42">
-        <v>-27.52294856224814</v>
+        <v>-26.50112104478736</v>
       </c>
       <c r="F42">
-        <v>-0.1502867033004081</v>
+        <v>0.2949143871297694</v>
       </c>
       <c r="G42">
-        <v>-4.111678847169912</v>
+        <v>-2.950743358549371</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.038117512704172</v>
       </c>
       <c r="E43">
-        <v>-27.5481314062048</v>
+        <v>-25.33814552098151</v>
       </c>
       <c r="F43">
-        <v>0.2253282118249998</v>
+        <v>0.5215391411876582</v>
       </c>
       <c r="G43">
-        <v>-4.44337564693165</v>
+        <v>-2.17518185506431</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.173316333942543</v>
       </c>
       <c r="E44">
-        <v>-27.20185711273427</v>
+        <v>-25.13183730214006</v>
       </c>
       <c r="F44">
-        <v>-0.02973191006878761</v>
+        <v>0.5500134422914884</v>
       </c>
       <c r="G44">
-        <v>-3.857101205745498</v>
+        <v>-2.584418252446858</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.389925667919003</v>
       </c>
       <c r="E45">
-        <v>-26.37130328040947</v>
+        <v>-25.3345997258335</v>
       </c>
       <c r="F45">
-        <v>0.03299703987560775</v>
+        <v>0.5002467854660997</v>
       </c>
       <c r="G45">
-        <v>-4.758013205529523</v>
+        <v>-2.490147157670571</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.666647003643816</v>
       </c>
       <c r="E46">
-        <v>-26.1274857113625</v>
+        <v>-24.22243368039371</v>
       </c>
       <c r="F46">
-        <v>-0.05201416483669151</v>
+        <v>0.3224377224551858</v>
       </c>
       <c r="G46">
-        <v>-4.900793724092749</v>
+        <v>-2.679030333413689</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.978464110650014</v>
       </c>
       <c r="E47">
-        <v>-26.07306703921232</v>
+        <v>-24.17240309955697</v>
       </c>
       <c r="F47">
-        <v>-0.1057304774386282</v>
+        <v>0.7276932799875655</v>
       </c>
       <c r="G47">
-        <v>-5.171268605196745</v>
+        <v>-2.924288789145055</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.305022524191751</v>
       </c>
       <c r="E48">
-        <v>-25.10621519620466</v>
+        <v>-22.89305032222799</v>
       </c>
       <c r="F48">
-        <v>0.02469514176475111</v>
+        <v>0.6821778046733439</v>
       </c>
       <c r="G48">
-        <v>-4.812031377093811</v>
+        <v>-2.748449162826666</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.622317598867812</v>
       </c>
       <c r="E49">
-        <v>-24.76545205560148</v>
+        <v>-23.20310135211115</v>
       </c>
       <c r="F49">
-        <v>0.1558596646914276</v>
+        <v>0.3770122236864228</v>
       </c>
       <c r="G49">
-        <v>-4.795071452296124</v>
+        <v>-3.172003669666561</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.914684328398413</v>
       </c>
       <c r="E50">
-        <v>-24.76944164120223</v>
+        <v>-21.81504708470206</v>
       </c>
       <c r="F50">
-        <v>0.1819259017553197</v>
+        <v>0.6717892490748353</v>
       </c>
       <c r="G50">
-        <v>-4.764038398410996</v>
+        <v>-3.015421486750113</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.170491436204194</v>
       </c>
       <c r="E51">
-        <v>-24.89006660334455</v>
+        <v>-22.32694125805511</v>
       </c>
       <c r="F51">
-        <v>0.2957361275933466</v>
+        <v>0.4651223508525951</v>
       </c>
       <c r="G51">
-        <v>-5.581137316777293</v>
+        <v>-3.489047994871484</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.37916705670515</v>
       </c>
       <c r="E52">
-        <v>-22.99409416276114</v>
+        <v>-20.9214614226645</v>
       </c>
       <c r="F52">
-        <v>0.2293979808749537</v>
+        <v>0.5596871168213811</v>
       </c>
       <c r="G52">
-        <v>-5.98360364853203</v>
+        <v>-2.98000196002545</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.539451955362147</v>
       </c>
       <c r="E53">
-        <v>-22.87710103677297</v>
+        <v>-20.36257980300786</v>
       </c>
       <c r="F53">
-        <v>0.164249369746981</v>
+        <v>0.851731358147958</v>
       </c>
       <c r="G53">
-        <v>-5.262474134803666</v>
+        <v>-3.284820440553844</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.650120569384085</v>
       </c>
       <c r="E54">
-        <v>-22.93022456535695</v>
+        <v>-20.76598985303316</v>
       </c>
       <c r="F54">
-        <v>0.3508730902910844</v>
+        <v>0.5934306629744189</v>
       </c>
       <c r="G54">
-        <v>-5.751312599677989</v>
+        <v>-4.12440789476841</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.716653801657549</v>
       </c>
       <c r="E55">
-        <v>-23.94323967239881</v>
+        <v>-19.32627475414456</v>
       </c>
       <c r="F55">
-        <v>0.1993207888467065</v>
+        <v>0.7603061046357821</v>
       </c>
       <c r="G55">
-        <v>-5.953951092136778</v>
+        <v>-3.708312047028493</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.749747092503419</v>
       </c>
       <c r="E56">
-        <v>-22.12584531279649</v>
+        <v>-19.69316718977201</v>
       </c>
       <c r="F56">
-        <v>0.2304988811532743</v>
+        <v>0.7214523599748741</v>
       </c>
       <c r="G56">
-        <v>-6.187155851559659</v>
+        <v>-3.855472417340176</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.756484507091686</v>
       </c>
       <c r="E57">
-        <v>-21.86989596188296</v>
+        <v>-18.9045832545503</v>
       </c>
       <c r="F57">
-        <v>0.1719854929217256</v>
+        <v>0.8796672204399685</v>
       </c>
       <c r="G57">
-        <v>-6.237102052110643</v>
+        <v>-4.661070500503045</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.75015870764947</v>
       </c>
       <c r="E58">
-        <v>-21.73218959578372</v>
+        <v>-18.26365021434868</v>
       </c>
       <c r="F58">
-        <v>0.6322976615137716</v>
+        <v>0.7550741361197004</v>
       </c>
       <c r="G58">
-        <v>-5.956596218022656</v>
+        <v>-4.225362980988485</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.743700943830135</v>
       </c>
       <c r="E59">
-        <v>-21.56937736978594</v>
+        <v>-18.33888175303811</v>
       </c>
       <c r="F59">
-        <v>0.4707618761308541</v>
+        <v>0.7345372514694951</v>
       </c>
       <c r="G59">
-        <v>-6.88863065642137</v>
+        <v>-4.970003989136753</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.744557403470674</v>
       </c>
       <c r="E60">
-        <v>-21.06127352917731</v>
+        <v>-17.62072464558369</v>
       </c>
       <c r="F60">
-        <v>0.5480137633811304</v>
+        <v>0.7661560352343522</v>
       </c>
       <c r="G60">
-        <v>-6.942178730519081</v>
+        <v>-5.26500008105013</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.762294017444847</v>
       </c>
       <c r="E61">
-        <v>-21.51206500274487</v>
+        <v>-17.90494978820112</v>
       </c>
       <c r="F61">
-        <v>0.1108519785951221</v>
+        <v>0.7270951987227443</v>
       </c>
       <c r="G61">
-        <v>-6.87536530044551</v>
+        <v>-5.467552499324898</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.799819130718409</v>
       </c>
       <c r="E62">
-        <v>-21.18012332950862</v>
+        <v>-16.98350042559436</v>
       </c>
       <c r="F62">
-        <v>0.5591097447416298</v>
+        <v>0.6361122934036634</v>
       </c>
       <c r="G62">
-        <v>-7.644405029218206</v>
+        <v>-5.453634965877803</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.85851704747732</v>
       </c>
       <c r="E63">
-        <v>-20.55301572045243</v>
+        <v>-16.69574760172496</v>
       </c>
       <c r="F63">
-        <v>0.6301497048383126</v>
+        <v>0.7845739560681964</v>
       </c>
       <c r="G63">
-        <v>-7.212325867614688</v>
+        <v>-5.427531314300649</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.939891266848933</v>
       </c>
       <c r="E64">
-        <v>-20.28784186798527</v>
+        <v>-16.81865491476714</v>
       </c>
       <c r="F64">
-        <v>0.5545810601505249</v>
+        <v>0.8293886325596497</v>
       </c>
       <c r="G64">
-        <v>-7.825786508769336</v>
+        <v>-6.115859942825915</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.037290289217727</v>
       </c>
       <c r="E65">
-        <v>-19.56441361678592</v>
+        <v>-16.20611540659362</v>
       </c>
       <c r="F65">
-        <v>0.3464057048877867</v>
+        <v>0.9187794157305499</v>
       </c>
       <c r="G65">
-        <v>-8.321461250182253</v>
+        <v>-5.462811798112662</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.146161555527772</v>
       </c>
       <c r="E66">
-        <v>-19.78329740794667</v>
+        <v>-16.43193681993412</v>
       </c>
       <c r="F66">
-        <v>0.3665118384885363</v>
+        <v>0.4580977952768552</v>
       </c>
       <c r="G66">
-        <v>-8.503266479562409</v>
+        <v>-5.792959262562021</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.262827813161425</v>
       </c>
       <c r="E67">
-        <v>-18.97326209135063</v>
+        <v>-16.33891290686855</v>
       </c>
       <c r="F67">
-        <v>0.3370882283410979</v>
+        <v>0.5090987195324153</v>
       </c>
       <c r="G67">
-        <v>-8.335507894905382</v>
+        <v>-6.327248207144997</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.377724864270859</v>
       </c>
       <c r="E68">
-        <v>-19.70135919925188</v>
+        <v>-15.79664172987205</v>
       </c>
       <c r="F68">
-        <v>0.4388042900982519</v>
+        <v>0.3067103389456344</v>
       </c>
       <c r="G68">
-        <v>-9.062516937511491</v>
+        <v>-5.82684931724754</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.485781943216261</v>
       </c>
       <c r="E69">
-        <v>-20.17285485598251</v>
+        <v>-16.5509496453297</v>
       </c>
       <c r="F69">
-        <v>0.4161327026510323</v>
+        <v>0.4091396250365988</v>
       </c>
       <c r="G69">
-        <v>-8.378644303282085</v>
+        <v>-6.542950112301751</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.57893012937246</v>
       </c>
       <c r="E70">
-        <v>-19.67359059663685</v>
+        <v>-15.49581973001651</v>
       </c>
       <c r="F70">
-        <v>0.4450327845999014</v>
+        <v>0.1707421134501236</v>
       </c>
       <c r="G70">
-        <v>-8.179081307629279</v>
+        <v>-6.637499292903336</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.650733668929168</v>
       </c>
       <c r="E71">
-        <v>-19.48125724858307</v>
+        <v>-15.95937244333768</v>
       </c>
       <c r="F71">
-        <v>0.4412943625110673</v>
+        <v>0.5043654281928188</v>
       </c>
       <c r="G71">
-        <v>-8.59947424347917</v>
+        <v>-6.399418099901109</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.698356708743868</v>
       </c>
       <c r="E72">
-        <v>-19.28352143103815</v>
+        <v>-16.14265337185013</v>
       </c>
       <c r="F72">
-        <v>0.09479821832886767</v>
+        <v>0.2413935692348934</v>
       </c>
       <c r="G72">
-        <v>-8.392899512374187</v>
+        <v>-5.903653973758631</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.714664115861929</v>
       </c>
       <c r="E73">
-        <v>-20.36820416772539</v>
+        <v>-16.35634753179808</v>
       </c>
       <c r="F73">
-        <v>0.2019541688202061</v>
+        <v>0.1211726080666011</v>
       </c>
       <c r="G73">
-        <v>-8.612312539080463</v>
+        <v>-6.638975796213851</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.696695466478238</v>
       </c>
       <c r="E74">
-        <v>-19.89817573657325</v>
+        <v>-16.2992661169314</v>
       </c>
       <c r="F74">
-        <v>-0.09462704077150368</v>
+        <v>0.2014679171547628</v>
       </c>
       <c r="G74">
-        <v>-8.284555288510459</v>
+        <v>-5.995289874285658</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.646745443496132</v>
       </c>
       <c r="E75">
-        <v>-18.59845841163178</v>
+        <v>-15.5576832134353</v>
       </c>
       <c r="F75">
-        <v>-0.03280763823538217</v>
+        <v>0.06716305340407336</v>
       </c>
       <c r="G75">
-        <v>-8.143228099438971</v>
+        <v>-6.652095488185982</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.564052951110504</v>
       </c>
       <c r="E76">
-        <v>-19.98514055141655</v>
+        <v>-16.9220082770442</v>
       </c>
       <c r="F76">
-        <v>0.04906736748991816</v>
+        <v>-0.2882529509714713</v>
       </c>
       <c r="G76">
-        <v>-8.788453425042926</v>
+        <v>-6.113860373320194</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.454174388575701</v>
       </c>
       <c r="E77">
-        <v>-19.9485051966945</v>
+        <v>-16.55566378677169</v>
       </c>
       <c r="F77">
-        <v>0.09472283689521291</v>
+        <v>0.02868124570702233</v>
       </c>
       <c r="G77">
-        <v>-8.211266431362073</v>
+        <v>-6.396203560182477</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.321923772324763</v>
       </c>
       <c r="E78">
-        <v>-20.77041417213865</v>
+        <v>-16.82144898322987</v>
       </c>
       <c r="F78">
-        <v>-0.3177701666354261</v>
+        <v>0.4738019844991282</v>
       </c>
       <c r="G78">
-        <v>-7.674858737633962</v>
+        <v>-6.219973289490454</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.173829992184706</v>
       </c>
       <c r="E79">
-        <v>-21.02414457078843</v>
+        <v>-17.63434629539876</v>
       </c>
       <c r="F79">
-        <v>-0.2357651072278862</v>
+        <v>0.1017283400206883</v>
       </c>
       <c r="G79">
-        <v>-7.953464318582408</v>
+        <v>-5.85001320438582</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.021177622493523</v>
       </c>
       <c r="E80">
-        <v>-20.9490896425853</v>
+        <v>-18.17628689379271</v>
       </c>
       <c r="F80">
-        <v>-0.4039825040817847</v>
+        <v>-0.2615936028471748</v>
       </c>
       <c r="G80">
-        <v>-8.040184058983616</v>
+        <v>-5.157586120482938</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.87035246690152</v>
       </c>
       <c r="E81">
-        <v>-20.45687168879558</v>
+        <v>-17.61716073653966</v>
       </c>
       <c r="F81">
-        <v>-0.4051471886501207</v>
+        <v>-0.2128657187448967</v>
       </c>
       <c r="G81">
-        <v>-8.155732029940799</v>
+        <v>-5.071005422994378</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.73064036075028</v>
       </c>
       <c r="E82">
-        <v>-22.69780063691327</v>
+        <v>-19.12448142388876</v>
       </c>
       <c r="F82">
-        <v>-0.6307596777417885</v>
+        <v>-0.5944920961124206</v>
       </c>
       <c r="G82">
-        <v>-7.820963043918618</v>
+        <v>-5.096241711640242</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.614957731276686</v>
       </c>
       <c r="E83">
-        <v>-22.97484814822854</v>
+        <v>-19.82202944613428</v>
       </c>
       <c r="F83">
-        <v>-0.7996041487196062</v>
+        <v>-0.5384348172301724</v>
       </c>
       <c r="G83">
-        <v>-7.704368940571026</v>
+        <v>-5.197895322969103</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.530002320706866</v>
       </c>
       <c r="E84">
-        <v>-23.79294867703224</v>
+        <v>-19.76450424081484</v>
       </c>
       <c r="F84">
-        <v>-0.4831603455435698</v>
+        <v>-0.4896083574069611</v>
       </c>
       <c r="G84">
-        <v>-7.570914228791926</v>
+        <v>-4.098618745017488</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.4882983195478</v>
       </c>
       <c r="E85">
-        <v>-24.26000190076134</v>
+        <v>-21.43463262568771</v>
       </c>
       <c r="F85">
-        <v>-0.6945795875556708</v>
+        <v>-0.4302450642201402</v>
       </c>
       <c r="G85">
-        <v>-7.69780743931219</v>
+        <v>-4.61067406575872</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.495197409342627</v>
       </c>
       <c r="E86">
-        <v>-25.53269329282503</v>
+        <v>-22.33877416063715</v>
       </c>
       <c r="F86">
-        <v>-0.6233341923430937</v>
+        <v>-0.5847654060687487</v>
       </c>
       <c r="G86">
-        <v>-7.648463758049354</v>
+        <v>-4.297102502824492</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.560753023815684</v>
       </c>
       <c r="E87">
-        <v>-27.3354742668046</v>
+        <v>-23.40957259601688</v>
       </c>
       <c r="F87">
-        <v>-0.7842221944170221</v>
+        <v>-0.8249298253253954</v>
       </c>
       <c r="G87">
-        <v>-7.233036640508369</v>
+        <v>-4.312456813035632</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.695495969318745</v>
       </c>
       <c r="E88">
-        <v>-27.97335058705103</v>
+        <v>-24.94708009110112</v>
       </c>
       <c r="F88">
-        <v>-0.8768444388262432</v>
+        <v>-0.8614790518717153</v>
       </c>
       <c r="G88">
-        <v>-6.970344851967201</v>
+        <v>-4.22524711189461</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.899957894433922</v>
       </c>
       <c r="E89">
-        <v>-29.03029189196729</v>
+        <v>-27.01245368736346</v>
       </c>
       <c r="F89">
-        <v>-0.599183969081877</v>
+        <v>-0.8951505300607095</v>
       </c>
       <c r="G89">
-        <v>-7.264824498776451</v>
+        <v>-4.190019596811226</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.180095149920528</v>
       </c>
       <c r="E90">
-        <v>-31.10859201728453</v>
+        <v>-27.81931907215413</v>
       </c>
       <c r="F90">
-        <v>-1.146319810263548</v>
+        <v>-1.034827356418554</v>
       </c>
       <c r="G90">
-        <v>-6.327751410066966</v>
+        <v>-4.216705904403291</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.536623814366735</v>
       </c>
       <c r="E91">
-        <v>-31.82747368058017</v>
+        <v>-29.93016986863851</v>
       </c>
       <c r="F91">
-        <v>-1.007454783960447</v>
+        <v>-1.129716014041834</v>
       </c>
       <c r="G91">
-        <v>-7.006946243449383</v>
+        <v>-3.950177193582107</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.963781930659753</v>
       </c>
       <c r="E92">
-        <v>-33.43814093749533</v>
+        <v>-31.4068395796667</v>
       </c>
       <c r="F92">
-        <v>-0.9914755767604444</v>
+        <v>-1.304837024830664</v>
       </c>
       <c r="G92">
-        <v>-7.682413402554579</v>
+        <v>-4.572182352773614</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.46133385889447</v>
       </c>
       <c r="E93">
-        <v>-35.32006831594395</v>
+        <v>-32.70377642156746</v>
       </c>
       <c r="F93">
-        <v>-1.468565498728792</v>
+        <v>-1.351393757970204</v>
       </c>
       <c r="G93">
-        <v>-7.747276921305519</v>
+        <v>-4.073657231651383</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.0116583699053</v>
       </c>
       <c r="E94">
-        <v>-37.39730877834339</v>
+        <v>-35.00987916760355</v>
       </c>
       <c r="F94">
-        <v>-1.260935209217096</v>
+        <v>-1.59407889923357</v>
       </c>
       <c r="G94">
-        <v>-7.76231010859935</v>
+        <v>-4.743016434236624</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.607095882534459</v>
       </c>
       <c r="E95">
-        <v>-39.66022799624234</v>
+        <v>-36.69162988101711</v>
       </c>
       <c r="F95">
-        <v>-1.584409366540691</v>
+        <v>-1.930930361744975</v>
       </c>
       <c r="G95">
-        <v>-7.119183668867294</v>
+        <v>-5.098320734238905</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.23779612899206</v>
       </c>
       <c r="E96">
-        <v>-42.23388204359961</v>
+        <v>-39.23664812298688</v>
       </c>
       <c r="F96">
-        <v>-1.555679099909396</v>
+        <v>-1.753535482435461</v>
       </c>
       <c r="G96">
-        <v>-7.48181751669352</v>
+        <v>-4.909450800677944</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.87713808105761</v>
       </c>
       <c r="E97">
-        <v>-44.78321818553569</v>
+        <v>-40.92285259058698</v>
       </c>
       <c r="F97">
-        <v>-1.732364068354711</v>
+        <v>-1.915514444378876</v>
       </c>
       <c r="G97">
-        <v>-7.650072683181439</v>
+        <v>-5.226094549872615</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.52037849898388</v>
       </c>
       <c r="E98">
-        <v>-46.60144804859242</v>
+        <v>-44.14034242998478</v>
       </c>
       <c r="F98">
-        <v>-1.798497608324612</v>
+        <v>-2.268649124927111</v>
       </c>
       <c r="G98">
-        <v>-8.172433732186422</v>
+        <v>-5.602460540595739</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.13758448076885</v>
       </c>
       <c r="E99">
-        <v>-49.74575774802627</v>
+        <v>-46.31177288750677</v>
       </c>
       <c r="F99">
-        <v>-1.705355149186433</v>
+        <v>-2.526829706827244</v>
       </c>
       <c r="G99">
-        <v>-8.026779660095107</v>
+        <v>-5.716972310799129</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.72947746608043</v>
       </c>
       <c r="E100">
-        <v>-52.32385196414806</v>
+        <v>-49.26174538913845</v>
       </c>
       <c r="F100">
-        <v>-2.170027015419413</v>
+        <v>-2.713482420230446</v>
       </c>
       <c r="G100">
-        <v>-8.11438662670084</v>
+        <v>-5.999970985678187</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.25646912283516</v>
       </c>
       <c r="E101">
-        <v>-53.19697684850047</v>
+        <v>-50.70124991398569</v>
       </c>
       <c r="F101">
-        <v>-2.125858465502144</v>
+        <v>-2.614827176026636</v>
       </c>
       <c r="G101">
-        <v>-8.468439540489276</v>
+        <v>-6.409641064526379</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.74912863712278</v>
       </c>
       <c r="E102">
-        <v>-56.4262316633702</v>
+        <v>-53.07390764251252</v>
       </c>
       <c r="F102">
-        <v>-2.374100295303488</v>
+        <v>-3.194611461654843</v>
       </c>
       <c r="G102">
-        <v>-8.762607996017836</v>
+        <v>-6.792657941237898</v>
       </c>
     </row>
   </sheetData>
